--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9255405855</v>
+        <v>46157.93109205576</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109205576</v>
+        <v>46157.93133518629</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93133518629</v>
+        <v>46157.93381319604</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93381319604</v>
+        <v>46157.93692744339</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93692744339</v>
+        <v>46158.28203773691</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203773691</v>
+        <v>46158.29650392778</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29650392778</v>
+        <v>46158.29804859397</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804859397</v>
+        <v>46158.33368232133</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33368232133</v>
+        <v>46158.37220126023</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220126023</v>
+        <v>46158.37274348096</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
